--- a/Data/EventData/SDGE_2022.xlsx
+++ b/Data/EventData/SDGE_2022.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sempra-my.sharepoint.com/personal/mstrutner_semprautilities_com/Documents/Ignitions/April Ignition Report/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dread\Downloads\Wildfire-Point-Process\Data\EventData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_3CD659EB459D0EBCD40975EAC2F72DBF939B52ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A05B1B91-9C0A-480F-9FC7-12A73A9EFA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33870" yWindow="1485" windowWidth="17280" windowHeight="10050" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Interactive (2022)" sheetId="3" r:id="rId1"/>
@@ -517,7 +517,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="157">
   <si>
     <t>Utility Name</t>
   </si>
@@ -791,12 +791,6 @@
   </si>
   <si>
     <t>230kv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blacked-out cells means N/A </t>
-  </si>
-  <si>
-    <t>This report includes SDG&amp;E’s preliminary assessment of the cause of the ignition; the cause of any ignition may remain subject to ongoing investigation by the appropriate fire investigation agency</t>
   </si>
   <si>
     <t>BVES</t>
@@ -1000,13 +994,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
     <numFmt numFmtId="165" formatCode="h:mm;@"/>
     <numFmt numFmtId="166" formatCode="0.0000000"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1184,14 +1178,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="54">
+  <fills count="53">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1491,14 +1479,8 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="40">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -1985,24 +1967,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2050,7 +2014,7 @@
     <xf numFmtId="0" fontId="1" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2248,43 +2212,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="49" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="53" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="53" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="53" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="53" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="53" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="53" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="53" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="53" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="53" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="53" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="53" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="53" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="53" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="49" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2481,7 +2408,9 @@
       </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{8F0459CB-820D-4E3C-8BCD-9CE6EB097BED}"/>
+  </tableStyles>
   <colors>
     <mruColors>
       <color rgb="FF00FFE5"/>
@@ -2500,9 +2429,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2540,9 +2469,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2575,26 +2504,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2627,26 +2539,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2823,7 +2718,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr defaultColWidth="9.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="2" customWidth="1"/>
@@ -2853,44 +2748,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="102" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="117" t="s">
+      <c r="B1" s="100"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="118"/>
-      <c r="F1" s="118"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="120" t="s">
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="121"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="123" t="s">
+      <c r="I1" s="108"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="110" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="124"/>
-      <c r="M1" s="124"/>
-      <c r="N1" s="124"/>
-      <c r="O1" s="125"/>
-      <c r="P1" s="126" t="s">
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="113" t="s">
         <v>4</v>
       </c>
-      <c r="Q1" s="127"/>
-      <c r="R1" s="128"/>
-      <c r="S1" s="109" t="s">
+      <c r="Q1" s="114"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="T1" s="110"/>
-      <c r="U1" s="111"/>
-      <c r="V1" s="111"/>
-      <c r="W1" s="112"/>
+      <c r="T1" s="97"/>
+      <c r="U1" s="98"/>
+      <c r="V1" s="98"/>
+      <c r="W1" s="99"/>
     </row>
     <row r="2" spans="1:23" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="116"/>
+      <c r="A2" s="103"/>
       <c r="B2" s="39" t="s">
         <v>6</v>
       </c>
@@ -3027,7 +2922,7 @@
         <v>44639</v>
       </c>
       <c r="C4" s="53">
-        <v>18.762499999999999</v>
+        <v>0.76249999999999996</v>
       </c>
       <c r="D4" s="54">
         <v>32.71</v>
@@ -3840,7 +3735,7 @@
       <c r="J16" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="K16" s="108"/>
+      <c r="K16" s="95"/>
       <c r="L16" s="88"/>
       <c r="M16" s="85" t="s">
         <v>32</v>
@@ -3905,7 +3800,7 @@
       <c r="J17" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="K17" s="108"/>
+      <c r="K17" s="95"/>
       <c r="L17" s="88"/>
       <c r="M17" s="85" t="s">
         <v>32</v>
@@ -4255,85 +4150,6 @@
       <c r="W22" s="18" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="23" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="101" t="s">
-        <v>91</v>
-      </c>
-      <c r="B23" s="95"/>
-      <c r="C23" s="96"/>
-      <c r="D23" s="97"/>
-      <c r="E23" s="97"/>
-      <c r="F23" s="98"/>
-      <c r="G23" s="98"/>
-      <c r="H23" s="97"/>
-      <c r="I23" s="97"/>
-      <c r="J23" s="97"/>
-      <c r="K23" s="98"/>
-      <c r="L23" s="98"/>
-      <c r="M23" s="99"/>
-      <c r="N23" s="97"/>
-      <c r="O23" s="97"/>
-      <c r="P23" s="97"/>
-      <c r="Q23" s="98"/>
-      <c r="R23" s="98"/>
-      <c r="S23" s="97"/>
-      <c r="T23" s="97"/>
-      <c r="U23" s="97"/>
-      <c r="V23" s="97"/>
-      <c r="W23" s="100"/>
-    </row>
-    <row r="24" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="101"/>
-      <c r="B24" s="95"/>
-      <c r="C24" s="96"/>
-      <c r="D24" s="97"/>
-      <c r="E24" s="97"/>
-      <c r="F24" s="98"/>
-      <c r="G24" s="98"/>
-      <c r="H24" s="97"/>
-      <c r="I24" s="97"/>
-      <c r="J24" s="97"/>
-      <c r="K24" s="98"/>
-      <c r="L24" s="98"/>
-      <c r="M24" s="99"/>
-      <c r="N24" s="97"/>
-      <c r="O24" s="97"/>
-      <c r="P24" s="97"/>
-      <c r="Q24" s="98"/>
-      <c r="R24" s="98"/>
-      <c r="S24" s="97"/>
-      <c r="T24" s="97"/>
-      <c r="U24" s="97"/>
-      <c r="V24" s="97"/>
-      <c r="W24" s="100"/>
-    </row>
-    <row r="25" spans="1:23" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A25" s="102" t="s">
-        <v>92</v>
-      </c>
-      <c r="B25" s="103"/>
-      <c r="C25" s="104"/>
-      <c r="D25" s="105"/>
-      <c r="E25" s="105"/>
-      <c r="F25" s="106"/>
-      <c r="G25" s="106"/>
-      <c r="H25" s="105"/>
-      <c r="I25" s="105"/>
-      <c r="J25" s="105"/>
-      <c r="K25" s="106"/>
-      <c r="L25" s="106"/>
-      <c r="M25" s="105"/>
-      <c r="N25" s="105"/>
-      <c r="O25" s="105"/>
-      <c r="P25" s="105"/>
-      <c r="Q25" s="106"/>
-      <c r="R25" s="106"/>
-      <c r="S25" s="105"/>
-      <c r="T25" s="105"/>
-      <c r="U25" s="105"/>
-      <c r="V25" s="105"/>
-      <c r="W25" s="107"/>
     </row>
   </sheetData>
   <dataConsolidate/>
@@ -4481,10 +4297,10 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>28</v>
@@ -4493,13 +4309,13 @@
         <v>71</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>60</v>
@@ -4514,33 +4330,33 @@
         <v>29</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="N2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="T2" s="1">
         <v>1</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>50</v>
@@ -4579,43 +4395,43 @@
         <v>33</v>
       </c>
       <c r="N3" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q3" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="T3" s="1">
         <f>T2+1</f>
         <v>2</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>79</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>50</v>
@@ -4624,37 +4440,37 @@
         <v>50</v>
       </c>
       <c r="K4" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="M4" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="N4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="S4" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="T4" s="1">
         <f t="shared" ref="T4:T18" si="0">T3+1</f>
         <v>3</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>69</v>
@@ -4672,37 +4488,37 @@
         <v>77</v>
       </c>
       <c r="K5" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="P5" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="S5" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="T5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>50</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>44</v>
@@ -4711,28 +4527,28 @@
         <v>69</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>57</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="T6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>63</v>
@@ -4741,26 +4557,26 @@
         <v>50</v>
       </c>
       <c r="I7" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="P7" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="S7" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="T7" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.3">
@@ -4768,7 +4584,7 @@
         <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>42</v>
@@ -4777,16 +4593,16 @@
         <v>69</v>
       </c>
       <c r="K8" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="P8" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="S8" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="T8" s="1">
         <f t="shared" si="0"/>
@@ -4795,19 +4611,19 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="G9" s="21" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>50</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="T9" s="1">
         <f t="shared" si="0"/>
@@ -4816,16 +4632,16 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="G10" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="M10" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="S10" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="T10" s="1">
         <f t="shared" si="0"/>
@@ -4835,10 +4651,10 @@
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="G11" s="22"/>
       <c r="M11" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="T11" s="1">
         <f t="shared" si="0"/>
@@ -4848,10 +4664,10 @@
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="G12" s="22"/>
       <c r="M12" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="T12" s="1">
         <f t="shared" si="0"/>
@@ -4861,10 +4677,10 @@
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="G13" s="22"/>
       <c r="M13" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="T13" s="1">
         <f t="shared" si="0"/>
@@ -4873,7 +4689,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="G14" s="22" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>37</v>
@@ -4906,7 +4722,7 @@
     <row r="17" spans="7:20" x14ac:dyDescent="0.3">
       <c r="G17" s="22"/>
       <c r="M17" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="T17" s="1">
         <f t="shared" si="0"/>
